--- a/DesignerConfigs/Datas/LuckySpin.xlsx
+++ b/DesignerConfigs/Datas/LuckySpin.xlsx
@@ -54,8 +54,10 @@
             <charset val="134"/>
           </rPr>
           <t>0：钱
-1：提示
-2：网格</t>
+1：加格
+2：清除
+3：锤子
+4：解锁</t>
         </r>
       </text>
     </comment>
@@ -1093,7 +1095,7 @@
     <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1119,7 +1121,7 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -1136,7 +1138,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1145,7 +1147,7 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,7 +1164,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:5">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>0</v>
@@ -1174,10 +1176,10 @@
         <v>10</v>
       </c>
       <c r="E6" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
         <v>1</v>
@@ -1192,43 +1194,43 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:5">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
         <v>2</v>
       </c>
       <c r="C8" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:5">
       <c r="A9" s="3"/>
       <c r="B9" s="3">
         <v>3</v>
       </c>
       <c r="C9" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="3"/>
       <c r="B10" s="3">
         <v>4</v>
       </c>
       <c r="C10" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -1237,7 +1239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:5">
       <c r="A11" s="3"/>
       <c r="B11" s="3">
         <v>5</v>
@@ -1246,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="D11" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E11" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">

--- a/DesignerConfigs/Datas/LuckySpin.xlsx
+++ b/DesignerConfigs/Datas/LuckySpin.xlsx
@@ -1095,7 +1095,7 @@
     <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1121,7 +1121,7 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1147,7 +1147,7 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
         <v>1</v>
@@ -1191,16 +1191,16 @@
         <v>1</v>
       </c>
       <c r="E7" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
         <v>2</v>
       </c>
       <c r="C8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -1209,57 +1209,55 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9" s="3"/>
       <c r="B9" s="3">
         <v>3</v>
       </c>
       <c r="C9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
       </c>
       <c r="E9" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="3"/>
       <c r="B10" s="3">
         <v>4</v>
       </c>
       <c r="C10" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E10" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="3"/>
       <c r="B11" s="3">
         <v>5</v>
       </c>
       <c r="C11" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E11" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6">

--- a/DesignerConfigs/Datas/LuckySpin.xlsx
+++ b/DesignerConfigs/Datas/LuckySpin.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ui配置|UIRes" sheetId="3" r:id="rId1"/>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="3">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3">
         <v>5</v>

--- a/DesignerConfigs/Datas/LuckySpin.xlsx
+++ b/DesignerConfigs/Datas/LuckySpin.xlsx
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E8" s="3">
         <v>2</v>
